--- a/assets/docs/lop5/Am nhac - Lop 5.xlsx
+++ b/assets/docs/lop5/Am nhac - Lop 5.xlsx
@@ -645,7 +645,7 @@
       <c r="D7" s="4" t="inlineStr"/>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Tổ chức hoạt động Vận dụng – Sáng tạo</t>
+          <t>Chủ đề 1: KHÚC CA NGÀY MỚI — Tổ chức hoạt động Vận dụng – Sáng tạo</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -784,7 +784,7 @@
       <c r="D11" s="4" t="inlineStr"/>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Tổ chức hoạt động Vận dụng – Sáng tạo</t>
+          <t>Chủ đề 2: GIAI ĐIỆU QUÊ HƯƠNG — Tổ chức hoạt động Vận dụng – Sáng tạo</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -801,7 +801,7 @@
         <is>
           <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở tiết tổng kết chủ đề “Giai điệu quê hương”, GV mở bản thu bài Lí đất giồng cùng một vài điệu lí khác của Nam Bộ; HS nghe
 Năng lực số Miền 3 (Cơ bản, bậc 2): Các nhóm dàn dựng tiết mục hát kết hợp gõ đệm và vận động; GV quay lại rồi chiếu chậm đoạn gõ đệm để mỗi nhóm nhìn thấy tay mình vào phách sớm hay…
-KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
+QPAN: Chọn bài hát ca ngợi quê hương, đất nước, hoà bình; liên hệ chủ quyền, quyền chủ quyền biển, đảo Việt Nam và gương dũng cảm cứu hộ, cứu nạn của cán bộ, chiến sĩ.</t>
         </is>
       </c>
     </row>
@@ -922,7 +922,7 @@
       <c r="D15" s="4" t="inlineStr"/>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Tổ chức hoạt động Vận dụng – Sáng tạo</t>
+          <t>Chủ đề 3: BAY VÀO TƯƠNG LAI — Tổ chức hoạt động Vận dụng – Sáng tạo</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -1060,7 +1060,7 @@
       <c r="D19" s="4" t="inlineStr"/>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Tổ chức hoạt động Vận dụng – Sáng tạo</t>
+          <t>Chủ đề 4: CHÀO MÙA XUÂN ĐẾN — Tổ chức hoạt động Vận dụng – Sáng tạo</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -1401,7 +1401,7 @@
       <c r="D29" s="4" t="inlineStr"/>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Tổ chức hoạt động Vận dụng – Sáng tạo</t>
+          <t>Chủ đề 6: ƯỚC MƠ TUỔI THƠ — Tổ chức hoạt động Vận dụng – Sáng tạo</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -1541,7 +1541,7 @@
       <c r="D33" s="4" t="inlineStr"/>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Tổ chức hoạt động Vận dụng – Sáng tạo</t>
+          <t>Chủ đề 7: ÂM NHẠC NƯỚC NGOÀI — Tổ chức hoạt động Vận dụng – Sáng tạo</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
